--- a/ai_digital_marketing/survey.xlsx
+++ b/ai_digital_marketing/survey.xlsx
@@ -1,15 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29929"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ai_digital_marketing\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50B004F8-2A51-486F-AD80-882BA3CB8043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
@@ -2209,8 +2215,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2273,13 +2279,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2317,7 +2331,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -2351,6 +2365,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -2385,9 +2400,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2560,11 +2576,17 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D201"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="22.44140625" customWidth="1"/>
+    <col min="2" max="2" width="75" customWidth="1"/>
+    <col min="3" max="3" width="42" customWidth="1"/>
+    <col min="4" max="4" width="41.109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2578,7 +2600,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>4</v>
       </c>
@@ -2592,7 +2614,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>5</v>
       </c>
@@ -2606,7 +2628,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -2620,7 +2642,7 @@
         <v>606</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>7</v>
       </c>
@@ -2634,7 +2656,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -2648,7 +2670,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>9</v>
       </c>
@@ -2662,7 +2684,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -2676,7 +2698,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>11</v>
       </c>
@@ -2690,7 +2712,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="10" spans="1:4">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>12</v>
       </c>
@@ -2704,7 +2726,7 @@
         <v>612</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>13</v>
       </c>
@@ -2718,7 +2740,7 @@
         <v>613</v>
       </c>
     </row>
-    <row r="12" spans="1:4">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>14</v>
       </c>
@@ -2732,7 +2754,7 @@
         <v>614</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>15</v>
       </c>
@@ -2746,7 +2768,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="14" spans="1:4">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>16</v>
       </c>
@@ -2760,7 +2782,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>17</v>
       </c>
@@ -2774,7 +2796,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -2788,7 +2810,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>19</v>
       </c>
@@ -2802,7 +2824,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="18" spans="1:4">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>20</v>
       </c>
@@ -2816,7 +2838,7 @@
         <v>618</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>21</v>
       </c>
@@ -2830,7 +2852,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>22</v>
       </c>
@@ -2844,7 +2866,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>23</v>
       </c>
@@ -2858,7 +2880,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="22" spans="1:4">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>24</v>
       </c>
@@ -2872,7 +2894,7 @@
         <v>622</v>
       </c>
     </row>
-    <row r="23" spans="1:4">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>25</v>
       </c>
@@ -2886,7 +2908,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="24" spans="1:4">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>26</v>
       </c>
@@ -2900,7 +2922,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="25" spans="1:4">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>27</v>
       </c>
@@ -2914,7 +2936,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="26" spans="1:4">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>28</v>
       </c>
@@ -2928,7 +2950,7 @@
         <v>624</v>
       </c>
     </row>
-    <row r="27" spans="1:4">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>29</v>
       </c>
@@ -2942,7 +2964,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="28" spans="1:4">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>30</v>
       </c>
@@ -2956,7 +2978,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="29" spans="1:4">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>31</v>
       </c>
@@ -2970,7 +2992,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="30" spans="1:4">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>32</v>
       </c>
@@ -2984,7 +3006,7 @@
         <v>628</v>
       </c>
     </row>
-    <row r="31" spans="1:4">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>33</v>
       </c>
@@ -2998,7 +3020,7 @@
         <v>629</v>
       </c>
     </row>
-    <row r="32" spans="1:4">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>34</v>
       </c>
@@ -3012,7 +3034,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="33" spans="1:4">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>35</v>
       </c>
@@ -3026,7 +3048,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="34" spans="1:4">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>36</v>
       </c>
@@ -3040,7 +3062,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="35" spans="1:4">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>37</v>
       </c>
@@ -3054,7 +3076,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="36" spans="1:4">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>38</v>
       </c>
@@ -3068,7 +3090,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="37" spans="1:4">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>39</v>
       </c>
@@ -3082,7 +3104,7 @@
         <v>634</v>
       </c>
     </row>
-    <row r="38" spans="1:4">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>40</v>
       </c>
@@ -3096,7 +3118,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="39" spans="1:4">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>41</v>
       </c>
@@ -3110,7 +3132,7 @@
         <v>636</v>
       </c>
     </row>
-    <row r="40" spans="1:4">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>42</v>
       </c>
@@ -3124,7 +3146,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="41" spans="1:4">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>43</v>
       </c>
@@ -3138,7 +3160,7 @@
         <v>638</v>
       </c>
     </row>
-    <row r="42" spans="1:4">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>44</v>
       </c>
@@ -3152,7 +3174,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="43" spans="1:4">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>45</v>
       </c>
@@ -3166,7 +3188,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="44" spans="1:4">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>46</v>
       </c>
@@ -3180,7 +3202,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="45" spans="1:4">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>47</v>
       </c>
@@ -3194,7 +3216,7 @@
         <v>641</v>
       </c>
     </row>
-    <row r="46" spans="1:4">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>48</v>
       </c>
@@ -3208,7 +3230,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="47" spans="1:4">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>49</v>
       </c>
@@ -3222,7 +3244,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="48" spans="1:4">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>50</v>
       </c>
@@ -3236,7 +3258,7 @@
         <v>643</v>
       </c>
     </row>
-    <row r="49" spans="1:4">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>51</v>
       </c>
@@ -3250,7 +3272,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="50" spans="1:4">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>52</v>
       </c>
@@ -3264,7 +3286,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="51" spans="1:4">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>53</v>
       </c>
@@ -3278,7 +3300,7 @@
         <v>645</v>
       </c>
     </row>
-    <row r="52" spans="1:4">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>54</v>
       </c>
@@ -3292,7 +3314,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="53" spans="1:4">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>55</v>
       </c>
@@ -3306,7 +3328,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="54" spans="1:4">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>56</v>
       </c>
@@ -3320,7 +3342,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="55" spans="1:4">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>57</v>
       </c>
@@ -3334,7 +3356,7 @@
         <v>647</v>
       </c>
     </row>
-    <row r="56" spans="1:4">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>58</v>
       </c>
@@ -3348,7 +3370,7 @@
         <v>648</v>
       </c>
     </row>
-    <row r="57" spans="1:4">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>59</v>
       </c>
@@ -3362,7 +3384,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="58" spans="1:4">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>60</v>
       </c>
@@ -3376,7 +3398,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="59" spans="1:4">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>61</v>
       </c>
@@ -3390,7 +3412,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="60" spans="1:4">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>62</v>
       </c>
@@ -3404,7 +3426,7 @@
         <v>650</v>
       </c>
     </row>
-    <row r="61" spans="1:4">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>63</v>
       </c>
@@ -3418,7 +3440,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="62" spans="1:4">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>64</v>
       </c>
@@ -3432,7 +3454,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="63" spans="1:4">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>65</v>
       </c>
@@ -3446,7 +3468,7 @@
         <v>651</v>
       </c>
     </row>
-    <row r="64" spans="1:4">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>66</v>
       </c>
@@ -3460,7 +3482,7 @@
         <v>652</v>
       </c>
     </row>
-    <row r="65" spans="1:4">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>67</v>
       </c>
@@ -3474,7 +3496,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="66" spans="1:4">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>68</v>
       </c>
@@ -3488,7 +3510,7 @@
         <v>654</v>
       </c>
     </row>
-    <row r="67" spans="1:4">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>69</v>
       </c>
@@ -3502,7 +3524,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="68" spans="1:4">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>70</v>
       </c>
@@ -3516,7 +3538,7 @@
         <v>656</v>
       </c>
     </row>
-    <row r="69" spans="1:4">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>71</v>
       </c>
@@ -3530,7 +3552,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="70" spans="1:4">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>72</v>
       </c>
@@ -3544,7 +3566,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="71" spans="1:4">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>73</v>
       </c>
@@ -3558,7 +3580,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="72" spans="1:4">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>74</v>
       </c>
@@ -3572,7 +3594,7 @@
         <v>660</v>
       </c>
     </row>
-    <row r="73" spans="1:4">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>75</v>
       </c>
@@ -3586,7 +3608,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="74" spans="1:4">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>76</v>
       </c>
@@ -3600,7 +3622,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="75" spans="1:4">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>77</v>
       </c>
@@ -3614,7 +3636,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="76" spans="1:4">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>78</v>
       </c>
@@ -3628,7 +3650,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="77" spans="1:4">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>79</v>
       </c>
@@ -3642,7 +3664,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="78" spans="1:4">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>80</v>
       </c>
@@ -3656,7 +3678,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="79" spans="1:4">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>81</v>
       </c>
@@ -3670,7 +3692,7 @@
         <v>662</v>
       </c>
     </row>
-    <row r="80" spans="1:4">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>82</v>
       </c>
@@ -3684,7 +3706,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="81" spans="1:4">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>83</v>
       </c>
@@ -3698,7 +3720,7 @@
         <v>664</v>
       </c>
     </row>
-    <row r="82" spans="1:4">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>84</v>
       </c>
@@ -3712,7 +3734,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="83" spans="1:4">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>85</v>
       </c>
@@ -3726,7 +3748,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="84" spans="1:4">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>86</v>
       </c>
@@ -3740,7 +3762,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="85" spans="1:4">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>87</v>
       </c>
@@ -3754,7 +3776,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="86" spans="1:4">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>88</v>
       </c>
@@ -3768,7 +3790,7 @@
         <v>642</v>
       </c>
     </row>
-    <row r="87" spans="1:4">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>89</v>
       </c>
@@ -3782,7 +3804,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="88" spans="1:4">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>90</v>
       </c>
@@ -3796,7 +3818,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="89" spans="1:4">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>91</v>
       </c>
@@ -3810,7 +3832,7 @@
         <v>668</v>
       </c>
     </row>
-    <row r="90" spans="1:4">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>92</v>
       </c>
@@ -3824,7 +3846,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="91" spans="1:4">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>93</v>
       </c>
@@ -3838,7 +3860,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="92" spans="1:4">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>94</v>
       </c>
@@ -3852,7 +3874,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="93" spans="1:4">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>95</v>
       </c>
@@ -3866,7 +3888,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="94" spans="1:4">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>96</v>
       </c>
@@ -3880,7 +3902,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="95" spans="1:4">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>97</v>
       </c>
@@ -3894,7 +3916,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="96" spans="1:4">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>98</v>
       </c>
@@ -3908,7 +3930,7 @@
         <v>672</v>
       </c>
     </row>
-    <row r="97" spans="1:4">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>99</v>
       </c>
@@ -3922,7 +3944,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="98" spans="1:4">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>100</v>
       </c>
@@ -3936,7 +3958,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="99" spans="1:4">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>101</v>
       </c>
@@ -3950,7 +3972,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="100" spans="1:4">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>102</v>
       </c>
@@ -3964,7 +3986,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="101" spans="1:4">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>103</v>
       </c>
@@ -3978,7 +4000,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="102" spans="1:4">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>104</v>
       </c>
@@ -3992,7 +4014,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="103" spans="1:4">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>105</v>
       </c>
@@ -4006,7 +4028,7 @@
         <v>675</v>
       </c>
     </row>
-    <row r="104" spans="1:4">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>106</v>
       </c>
@@ -4020,7 +4042,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="105" spans="1:4">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>107</v>
       </c>
@@ -4034,7 +4056,7 @@
         <v>677</v>
       </c>
     </row>
-    <row r="106" spans="1:4">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>108</v>
       </c>
@@ -4048,7 +4070,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="107" spans="1:4">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>109</v>
       </c>
@@ -4062,7 +4084,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="108" spans="1:4">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>110</v>
       </c>
@@ -4076,7 +4098,7 @@
         <v>679</v>
       </c>
     </row>
-    <row r="109" spans="1:4">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>111</v>
       </c>
@@ -4090,7 +4112,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="110" spans="1:4">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>112</v>
       </c>
@@ -4104,7 +4126,7 @@
         <v>680</v>
       </c>
     </row>
-    <row r="111" spans="1:4">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>113</v>
       </c>
@@ -4118,7 +4140,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="112" spans="1:4">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>114</v>
       </c>
@@ -4132,7 +4154,7 @@
         <v>681</v>
       </c>
     </row>
-    <row r="113" spans="1:4">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>115</v>
       </c>
@@ -4146,7 +4168,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="114" spans="1:4">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>116</v>
       </c>
@@ -4160,7 +4182,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="115" spans="1:4">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>117</v>
       </c>
@@ -4174,7 +4196,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="116" spans="1:4">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>118</v>
       </c>
@@ -4188,7 +4210,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="117" spans="1:4">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>119</v>
       </c>
@@ -4202,7 +4224,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="118" spans="1:4">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>120</v>
       </c>
@@ -4216,7 +4238,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="119" spans="1:4">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>121</v>
       </c>
@@ -4230,7 +4252,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="120" spans="1:4">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>122</v>
       </c>
@@ -4244,7 +4266,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="121" spans="1:4">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>123</v>
       </c>
@@ -4258,7 +4280,7 @@
         <v>685</v>
       </c>
     </row>
-    <row r="122" spans="1:4">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>124</v>
       </c>
@@ -4272,7 +4294,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="123" spans="1:4">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>125</v>
       </c>
@@ -4286,7 +4308,7 @@
         <v>686</v>
       </c>
     </row>
-    <row r="124" spans="1:4">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>126</v>
       </c>
@@ -4300,7 +4322,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="125" spans="1:4">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>127</v>
       </c>
@@ -4314,7 +4336,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="126" spans="1:4">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>128</v>
       </c>
@@ -4328,7 +4350,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="127" spans="1:4">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>129</v>
       </c>
@@ -4342,7 +4364,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="128" spans="1:4">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>130</v>
       </c>
@@ -4356,7 +4378,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="129" spans="1:4">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>131</v>
       </c>
@@ -4370,7 +4392,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="130" spans="1:4">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>132</v>
       </c>
@@ -4384,7 +4406,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="131" spans="1:4">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>133</v>
       </c>
@@ -4398,7 +4420,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="132" spans="1:4">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>134</v>
       </c>
@@ -4412,7 +4434,7 @@
         <v>689</v>
       </c>
     </row>
-    <row r="133" spans="1:4">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>135</v>
       </c>
@@ -4426,7 +4448,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="134" spans="1:4">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>136</v>
       </c>
@@ -4440,7 +4462,7 @@
         <v>690</v>
       </c>
     </row>
-    <row r="135" spans="1:4">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>137</v>
       </c>
@@ -4454,7 +4476,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="136" spans="1:4">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>138</v>
       </c>
@@ -4468,7 +4490,7 @@
         <v>691</v>
       </c>
     </row>
-    <row r="137" spans="1:4">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>139</v>
       </c>
@@ -4482,7 +4504,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="138" spans="1:4">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>140</v>
       </c>
@@ -4496,7 +4518,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="139" spans="1:4">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>141</v>
       </c>
@@ -4510,7 +4532,7 @@
         <v>694</v>
       </c>
     </row>
-    <row r="140" spans="1:4">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>142</v>
       </c>
@@ -4524,7 +4546,7 @@
         <v>695</v>
       </c>
     </row>
-    <row r="141" spans="1:4">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>143</v>
       </c>
@@ -4538,7 +4560,7 @@
         <v>696</v>
       </c>
     </row>
-    <row r="142" spans="1:4">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>144</v>
       </c>
@@ -4552,7 +4574,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="143" spans="1:4">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>145</v>
       </c>
@@ -4566,7 +4588,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="144" spans="1:4">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>146</v>
       </c>
@@ -4580,7 +4602,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="145" spans="1:4">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>147</v>
       </c>
@@ -4594,7 +4616,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="146" spans="1:4">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>148</v>
       </c>
@@ -4608,7 +4630,7 @@
         <v>699</v>
       </c>
     </row>
-    <row r="147" spans="1:4">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>149</v>
       </c>
@@ -4622,7 +4644,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="148" spans="1:4">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>150</v>
       </c>
@@ -4636,7 +4658,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="149" spans="1:4">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>151</v>
       </c>
@@ -4650,7 +4672,7 @@
         <v>700</v>
       </c>
     </row>
-    <row r="150" spans="1:4">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>152</v>
       </c>
@@ -4664,7 +4686,7 @@
         <v>701</v>
       </c>
     </row>
-    <row r="151" spans="1:4">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>153</v>
       </c>
@@ -4678,7 +4700,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="152" spans="1:4">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>154</v>
       </c>
@@ -4692,7 +4714,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="153" spans="1:4">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>155</v>
       </c>
@@ -4706,7 +4728,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="154" spans="1:4">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>156</v>
       </c>
@@ -4720,7 +4742,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="155" spans="1:4">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>157</v>
       </c>
@@ -4734,7 +4756,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="156" spans="1:4">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>158</v>
       </c>
@@ -4748,7 +4770,7 @@
         <v>705</v>
       </c>
     </row>
-    <row r="157" spans="1:4">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>159</v>
       </c>
@@ -4762,7 +4784,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="158" spans="1:4">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>160</v>
       </c>
@@ -4776,7 +4798,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="159" spans="1:4">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>161</v>
       </c>
@@ -4790,7 +4812,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="160" spans="1:4">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>162</v>
       </c>
@@ -4804,7 +4826,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="161" spans="1:4">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>163</v>
       </c>
@@ -4818,7 +4840,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="162" spans="1:4">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>164</v>
       </c>
@@ -4832,7 +4854,7 @@
         <v>706</v>
       </c>
     </row>
-    <row r="163" spans="1:4">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>165</v>
       </c>
@@ -4846,7 +4868,7 @@
         <v>707</v>
       </c>
     </row>
-    <row r="164" spans="1:4">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>166</v>
       </c>
@@ -4860,7 +4882,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="165" spans="1:4">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>167</v>
       </c>
@@ -4874,7 +4896,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="166" spans="1:4">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>168</v>
       </c>
@@ -4888,7 +4910,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="167" spans="1:4">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>169</v>
       </c>
@@ -4902,7 +4924,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="168" spans="1:4">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>170</v>
       </c>
@@ -4916,7 +4938,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="169" spans="1:4">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>171</v>
       </c>
@@ -4930,7 +4952,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="170" spans="1:4">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>172</v>
       </c>
@@ -4944,7 +4966,7 @@
         <v>711</v>
       </c>
     </row>
-    <row r="171" spans="1:4">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>173</v>
       </c>
@@ -4958,7 +4980,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="172" spans="1:4">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>174</v>
       </c>
@@ -4972,7 +4994,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="173" spans="1:4">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>175</v>
       </c>
@@ -4986,7 +5008,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="174" spans="1:4">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>176</v>
       </c>
@@ -5000,7 +5022,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="175" spans="1:4">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>177</v>
       </c>
@@ -5014,7 +5036,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="176" spans="1:4">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>178</v>
       </c>
@@ -5028,7 +5050,7 @@
         <v>716</v>
       </c>
     </row>
-    <row r="177" spans="1:4">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>179</v>
       </c>
@@ -5042,7 +5064,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="178" spans="1:4">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>180</v>
       </c>
@@ -5056,7 +5078,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="179" spans="1:4">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>181</v>
       </c>
@@ -5070,7 +5092,7 @@
         <v>718</v>
       </c>
     </row>
-    <row r="180" spans="1:4">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>182</v>
       </c>
@@ -5084,7 +5106,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="181" spans="1:4">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>183</v>
       </c>
@@ -5098,7 +5120,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="182" spans="1:4">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>184</v>
       </c>
@@ -5112,7 +5134,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="183" spans="1:4">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>185</v>
       </c>
@@ -5126,7 +5148,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="184" spans="1:4">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>186</v>
       </c>
@@ -5140,7 +5162,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="185" spans="1:4">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>187</v>
       </c>
@@ -5154,7 +5176,7 @@
         <v>721</v>
       </c>
     </row>
-    <row r="186" spans="1:4">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>188</v>
       </c>
@@ -5168,7 +5190,7 @@
         <v>632</v>
       </c>
     </row>
-    <row r="187" spans="1:4">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>189</v>
       </c>
@@ -5182,7 +5204,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="188" spans="1:4">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>190</v>
       </c>
@@ -5196,7 +5218,7 @@
         <v>723</v>
       </c>
     </row>
-    <row r="189" spans="1:4">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>191</v>
       </c>
@@ -5210,7 +5232,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="190" spans="1:4">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>192</v>
       </c>
@@ -5224,7 +5246,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="191" spans="1:4">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>193</v>
       </c>
@@ -5238,7 +5260,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="192" spans="1:4">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>194</v>
       </c>
@@ -5252,7 +5274,7 @@
         <v>620</v>
       </c>
     </row>
-    <row r="193" spans="1:4">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>195</v>
       </c>
@@ -5266,7 +5288,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="194" spans="1:4">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>196</v>
       </c>
@@ -5280,7 +5302,7 @@
         <v>726</v>
       </c>
     </row>
-    <row r="195" spans="1:4">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>197</v>
       </c>
@@ -5294,7 +5316,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="196" spans="1:4">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>198</v>
       </c>
@@ -5308,7 +5330,7 @@
         <v>728</v>
       </c>
     </row>
-    <row r="197" spans="1:4">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>199</v>
       </c>
@@ -5322,7 +5344,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="198" spans="1:4">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>200</v>
       </c>
@@ -5336,7 +5358,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="199" spans="1:4">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>201</v>
       </c>
@@ -5350,7 +5372,7 @@
         <v>609</v>
       </c>
     </row>
-    <row r="200" spans="1:4">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>202</v>
       </c>
@@ -5364,7 +5386,7 @@
         <v>610</v>
       </c>
     </row>
-    <row r="201" spans="1:4">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>203</v>
       </c>
